--- a/tests/integration_workspace/dashboard_full_pipeline/output/FINAL_REPORT.xlsx
+++ b/tests/integration_workspace/dashboard_full_pipeline/output/FINAL_REPORT.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6 sec</t>
+          <t>10 sec</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,17 @@
           <t>SKU-APPLE</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SVO shampoo apple 1 l</t>
+        </is>
+      </c>
       <c r="D2" t="n">
         <v>35.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-05T18:55:03.233973+00:00</t>
+          <t>2026-08-06T16:37:00.557317+00:00</t>
         </is>
       </c>
     </row>
@@ -604,12 +609,17 @@
           <t>SKU-LIME</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SVO shampoo lime 1 l</t>
+        </is>
+      </c>
       <c r="D3" t="n">
         <v>39</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-05T18:55:03.233973+00:00</t>
+          <t>2026-08-06T16:37:00.557317+00:00</t>
         </is>
       </c>
     </row>
@@ -999,7 +1009,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DATE              : 05.08.2026</t>
+          <t>DATE              : 06.08.2026</t>
         </is>
       </c>
     </row>

--- a/tests/integration_workspace/dashboard_full_pipeline/output/FINAL_REPORT.xlsx
+++ b/tests/integration_workspace/dashboard_full_pipeline/output/FINAL_REPORT.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10 sec</t>
+          <t>7 sec</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-06T16:37:00.557317+00:00</t>
+          <t>2026-09-03T09:07:46.189545+00:00</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-06T16:37:00.557317+00:00</t>
+          <t>2026-09-03T09:07:46.189545+00:00</t>
         </is>
       </c>
     </row>
@@ -703,139 +703,175 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>НАИМЕНОВАНИЕ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Тип товара</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Бренд</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Variant</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Объем</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>MATCH_STATUS</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>MATCH_SKU</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>MATCH_MASTER_NAME</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>MATCH_CONFIDENCE</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>MATCH_REASONS</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Отгружено</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Шампунь SVO APPLE 1 л</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>SKU-APPLE</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Шампунь</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>SVO</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>APPLE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>1 л</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>SKU-APPLE</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SVO SHAMPUN APPLE 1 л</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>100</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Шампунь SVO LIME 1 л</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>SKU-LIME</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Шампунь</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>SVO</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>LIME</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>1 л</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>SKU-LIME</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SVO SHAMPUN LIME 1 л</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>100</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1009,7 +1045,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DATE              : 06.08.2026</t>
+          <t>DATE              : 03.09.2026</t>
         </is>
       </c>
     </row>
